--- a/A00_index.xlsx
+++ b/A00_index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0151B2-6936-4FB2-91EF-0F00F284B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DB5F46-AB6F-4069-AFB5-25C1A5F7C8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,26 @@
     <sheet name="C02_javascript" sheetId="3" r:id="rId4"/>
     <sheet name="C04_java" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>C00_html</t>
   </si>
@@ -117,6 +126,126 @@
   </si>
   <si>
     <t>C:\lect\C00_html\html900_영역\html902_시맨틱태그_영역_인라인블록_ver001+250709.html</t>
+  </si>
+  <si>
+    <t>section05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Application4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dementional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배열 예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배열예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차원 배열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chap05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얕은 복사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얕은복사 활용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깊은 복사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깊은복사 활용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정렬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클래스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Member</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클래스를 쓰는 이유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">직접접근 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section02 encaptsulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster 필드 변수의 이름을 변경시 main method를 다 바꿔야한다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직접 접근은 private로 막고 public 메소드 getter setter를 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -629,9 +758,177 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5F1543-67CE-4086-B440-1841205D1B1D}">
-  <dimension ref="A1"/>
+  <dimension ref="E2:I21"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/A00_index.xlsx
+++ b/A00_index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DB5F46-AB6F-4069-AFB5-25C1A5F7C8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D335DB76-CA71-4159-A3A8-C3CE4543484E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>C00_html</t>
   </si>
@@ -245,6 +245,58 @@
   </si>
   <si>
     <t>직접 접근은 private로 막고 public 메소드 getter setter를 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chap06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section03 추상화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Car</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CarRacer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복잡한 로직</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추상화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">실행 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 추상화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dto 폴더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section04 생성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성자를 이용한 초기화, 설정자를 이용한 초기화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UserDTO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -758,7 +810,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5F1543-67CE-4086-B440-1841205D1B1D}">
-  <dimension ref="E2:I21"/>
+  <dimension ref="E2:I32"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
@@ -771,6 +823,11 @@
         <v>39</v>
       </c>
     </row>
+    <row r="3" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="4" spans="5:9" x14ac:dyDescent="0.4">
       <c r="E4" t="s">
         <v>29</v>
@@ -896,7 +953,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="5:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="5:9" x14ac:dyDescent="0.4">
       <c r="E17" t="s">
         <v>32</v>
       </c>
@@ -907,7 +964,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="5:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="5:9" x14ac:dyDescent="0.4">
       <c r="E18" t="s">
         <v>34</v>
       </c>
@@ -915,17 +972,83 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="5:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="5:9" x14ac:dyDescent="0.4">
       <c r="E20" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="5:8" x14ac:dyDescent="0.4">
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" x14ac:dyDescent="0.4">
       <c r="E21" t="s">
         <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>46</v>
+      </c>
+      <c r="H21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H22" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="H32" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/A00_index.xlsx
+++ b/A00_index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D335DB76-CA71-4159-A3A8-C3CE4543484E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12B308-26ED-4C74-AD6D-20920F6D9E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="88">
   <si>
     <t>C00_html</t>
   </si>
@@ -297,6 +297,70 @@
   </si>
   <si>
     <t>UserDTO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section05 오버로딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overloading</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parametertest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RectAngle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">객체는 주소값을 넘긴다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버로딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>section06 기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>singleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EagerSingleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LazySiongleton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이른 초기화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게으른 생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>staticKeyword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaticFieldTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaticMethodTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -810,7 +874,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5F1543-67CE-4086-B440-1841205D1B1D}">
-  <dimension ref="E2:I32"/>
+  <dimension ref="E2:I50"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
@@ -1051,6 +1115,91 @@
         <v>71</v>
       </c>
     </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H34" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H35" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H38" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H44" t="s">
+        <v>80</v>
+      </c>
+      <c r="I44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H45" t="s">
+        <v>81</v>
+      </c>
+      <c r="I45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H49" t="s">
+        <v>85</v>
+      </c>
+      <c r="I49" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="50" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H50" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/A00_index.xlsx
+++ b/A00_index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12B308-26ED-4C74-AD6D-20920F6D9E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA528F6-465B-416A-AE65-8D84C82C462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="94">
   <si>
     <t>C00_html</t>
   </si>
@@ -324,10 +324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>section06 기타</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>singleton</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -361,6 +357,34 @@
   </si>
   <si>
     <t>static</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemeberFinder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemberRegister</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemberRepository</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemberService</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chap07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버라이딩 성립요건</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +898,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5F1543-67CE-4086-B440-1841205D1B1D}">
-  <dimension ref="E2:I50"/>
+  <dimension ref="E2:M52"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="11.59765625" bestFit="1" customWidth="1"/>
@@ -1017,7 +1041,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="5:13" x14ac:dyDescent="0.4">
       <c r="E17" t="s">
         <v>32</v>
       </c>
@@ -1028,7 +1052,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="5:13" x14ac:dyDescent="0.4">
       <c r="E18" t="s">
         <v>34</v>
       </c>
@@ -1036,12 +1060,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="5:13" x14ac:dyDescent="0.4">
       <c r="E20" t="s">
         <v>45</v>
       </c>
@@ -1052,7 +1076,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="5:13" x14ac:dyDescent="0.4">
       <c r="E21" t="s">
         <v>30</v>
       </c>
@@ -1066,7 +1090,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H22" t="s">
         <v>62</v>
       </c>
@@ -1074,35 +1098,55 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H24" t="s">
         <v>67</v>
       </c>
       <c r="I24" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="M24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H25" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="M25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.4">
+      <c r="M26" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H27" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="28" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="M27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H28" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="M28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H29" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" spans="5:9" x14ac:dyDescent="0.4">
+      <c r="M29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H31" t="s">
         <v>30</v>
       </c>
@@ -1110,9 +1154,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="5:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="5:13" x14ac:dyDescent="0.4">
       <c r="H32" t="s">
         <v>71</v>
+      </c>
+      <c r="M32" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="8:9" x14ac:dyDescent="0.4">
@@ -1148,12 +1195,12 @@
     </row>
     <row r="41" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H41" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="8:9" x14ac:dyDescent="0.4">
@@ -1163,23 +1210,23 @@
     </row>
     <row r="44" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="8:9" x14ac:dyDescent="0.4">
@@ -1189,15 +1236,20 @@
     </row>
     <row r="49" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H50" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H52" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
